--- a/output/2026-10-03_20_Malesia_Perlis_ATEX_Equipment_Services.xlsx
+++ b/output/2026-10-03_20_Malesia_Perlis_ATEX_Equipment_Services.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato via WebFetch diretto sul sito ufficiale: sede confermata (No. 15B, Jalan Anggerik Vanilla N31/N, Kota Kemuning, 40460 Shah Alam, Selangor; reg. 200401014438). Certificazioni ATEX/IECEx esplicitamente dichiarate. Nessuna sede diretta a Perlis; è distributore nazionale, copertura specifica del nord Malaysia/Perlis non confermata esplicitamente.</t>
+          <t>Verificato via WebFetch diretto sul sito ufficiale: sede confermata (No. 15B, Jalan Anggerik Vanilla N31/N, Kota Kemuning, 40460 Shah Alam, Selangor; reg. 200401014438). Certificazioni ATEX/IECEx esplicitamente dichiarate. Nessuna sede diretta a Perlis; è distributore nazionale, copertura specifica del nord Malaysia/Perlis non confermata esplicitamente. [DUPLICATO — vedi anche: 2026-10-01_03_Malesia_Kedah_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -516,7 +516,6 @@
           <t>See Kwong Electric (KL) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Puchong, Selangor (distributore nazionale) — nessuna sede a Perlis</t>
@@ -527,11 +526,9 @@
           <t>Distributore di prodotti per aree pericolose: explosion-proof lighting, cable glands, industrial fuses, plug&amp;socket, certificati ATEX/IECEx/IEC/CSA, per oil&amp;gas, raffinerie, manifattura</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nessun sito ufficiale individuato con certezza; esistenza e attività confermate via WebSearch (profili aziendali su maukerja.my e sgpgrid.com): azienda costituita a luglio 1982, sede a 14 &amp; 16, Jalan TPP 5/2, Taman Perindustrian Puchong, Puchong, Selangor. Prodotti certificati ATEX/IECEx confermati da fonte indipendente. Telefono ed email non reperiti da fonte verificabile, lasciati vuoti per non inventare dati. Copertura Perlis/nord Malaysia non confermata.</t>
+          <t>Nessun sito ufficiale individuato con certezza; esistenza e attività confermate via WebSearch (profili aziendali su maukerja.my e sgpgrid.com): azienda costituita a luglio 1982, sede a 14 &amp; 16, Jalan TPP 5/2, Taman Perindustrian Puchong, Puchong, Selangor. Prodotti certificati ATEX/IECEx confermati da fonte indipendente. Telefono ed email non reperiti da fonte verificabile, lasciati vuoti per non inventare dati. Copertura Perlis/nord Malaysia non confermata. [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +570,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Verificato via WebFetch sul sito ufficiale: prodotti explosion-proof confermati esplicitamente (Eaton Crouse-Hinds, CEAG, Thuba, WINNEX), ISO 9001:2015 (TÜV SÜD). Presenza ufficio Penang confermata anche da fonte indipendente (Malaysian-German Chamber of Commerce). Copertura diretta Perlis non confermata, ma l'ufficio Penang è il più vicino geograficamente.</t>
+          <t>Verificato via WebFetch sul sito ufficiale: prodotti explosion-proof confermati esplicitamente (Eaton Crouse-Hinds, CEAG, Thuba, WINNEX), ISO 9001:2015 (TÜV SÜD). Presenza ufficio Penang confermata anche da fonte indipendente (Malaysian-German Chamber of Commerce). Copertura diretta Perlis non confermata, ma l'ufficio Penang è il più vicino geograficamente. [DUPLICATO — vedi anche: 2026-10-02_18_Malesia_Negeri_Sembilan_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,10 +605,9 @@
           <t>+604 642 5004</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Multinazionale verificata via WebFetch (presenza Malaysia confermata, sede Penang con prefisso telefonico 04 coerente). Prodotti ATEX-compliant per gestione polveri combustibili confermati tramite WebSearch sul catalogo globale Camfil (non trovata pagina Malaysia-specifica che li elenchi esplicitamente, ma è lo stesso gruppo societario con medesimo portafoglio prodotti). Email generica non reperita. Copertura diretta Perlis non confermata.</t>
+          <t>Multinazionale verificata via WebFetch (presenza Malaysia confermata, sede Penang con prefisso telefonico 04 coerente). Prodotti ATEX-compliant per gestione polveri combustibili confermati tramite WebSearch sul catalogo globale Camfil (non trovata pagina Malaysia-specifica che li elenchi esplicitamente, ma è lo stesso gruppo societario con medesimo portafoglio prodotti). Email generica non reperita. Copertura diretta Perlis non confermata. [DUPLICATO — vedi anche: 2026-10-03_17_Malesia_Perlis_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
